--- a/base_prov_co/farmatodo/farmatodo_abbott_2026_10_01.xlsx
+++ b/base_prov_co/farmatodo/farmatodo_abbott_2026_10_01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Farmatodo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Farmatodo'!$A$1:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Farmatodo'!$A$1:$R$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,65 +471,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoría</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>url_imagen</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -546,27 +551,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -577,14 +580,15 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1050596-ensure-advance-vainilla</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -601,27 +605,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -632,14 +634,15 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232300088-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -656,27 +659,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>7703186033031</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -687,14 +688,15 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/233000052-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -711,27 +713,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>8427030008592</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -742,14 +742,15 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1043564-ensure-advance-vainilla</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -766,27 +767,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -797,14 +796,15 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232350085-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -821,27 +821,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -852,14 +850,15 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/106461753-ensure-advance-fresa</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -876,27 +875,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>7703186998262</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -907,14 +904,15 @@
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/238000246-ensure-advance-400-gr-ensure-advance-liquido-sabor-vainilla-oferta-x-2-und</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -931,27 +929,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -962,14 +958,15 @@
       <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232350077-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -986,27 +983,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1017,14 +1012,15 @@
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1017009-ensure-vainilla-x400g</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1041,27 +1037,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1072,14 +1066,15 @@
       <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850038-ensure-sabor-vainilla</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1096,27 +1091,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>7703186031433</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1127,14 +1120,15 @@
       <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200192-ensure-clinical-rpb-x-220-ml</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1151,27 +1145,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1182,14 +1174,15 @@
       <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850046-ensure-advance-sabor</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1206,27 +1199,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1237,14 +1228,15 @@
       <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239100214-ensure-advance-cafe-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1261,27 +1253,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>8710428011848</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1292,14 +1282,15 @@
       <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650228-ensure-advance-chocolate</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1316,27 +1307,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>8710428017987</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1347,14 +1336,15 @@
       <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/229350210-ensure-plus-rpb-hn-x220ml</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1371,27 +1361,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>7703186069917</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1402,14 +1390,15 @@
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1015930-pulmocare-x237ml</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1426,27 +1415,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>8710428022790</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1457,14 +1444,15 @@
       <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200379-alimento-liquido-prosure</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1481,27 +1469,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1512,14 +1498,15 @@
       <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/283000464-glucerna-vainilla-850</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1536,27 +1523,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1567,14 +1552,15 @@
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1050402-glucerna-vainilla</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1591,27 +1577,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1622,14 +1606,15 @@
       <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/243900265-glucerna-vainilla-oferta-850gr-400gr-x-2-latas</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1646,27 +1631,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1677,14 +1660,15 @@
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/107611792-oft-glucerna-vainilla</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1701,27 +1685,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>7703186190376</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1732,14 +1714,15 @@
       <c r="M23" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239150289-glucerna-liquido-sabor-vainilla-y-fresa-pack-x-8-und</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1756,27 +1739,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1787,14 +1768,15 @@
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1052904-glucerna-fresa</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1811,27 +1793,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1842,14 +1822,15 @@
       <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1026565-glucerna-sr-vainilla</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1866,27 +1847,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1897,14 +1876,15 @@
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/243950238-glucerna-abbott-sabor-capuchino-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1921,27 +1901,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>8710428024299</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1952,14 +1930,15 @@
       <c r="M27" t="n">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200256-glucerna-16-kcal-frasco</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -1976,27 +1955,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2007,14 +1984,15 @@
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036529-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2031,27 +2009,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2062,14 +2038,15 @@
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650210-pedialyte-max-60-suero</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2086,27 +2063,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2117,14 +2092,15 @@
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036528-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2141,27 +2117,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2172,14 +2146,15 @@
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650201-pedialyte-max-60-suero</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2196,27 +2171,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2227,14 +2200,15 @@
       <c r="M32" t="n">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051669-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2251,27 +2225,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2282,14 +2254,15 @@
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036531-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2306,27 +2279,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2337,14 +2308,15 @@
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051671-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2361,27 +2333,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2392,14 +2362,15 @@
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051672-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2416,27 +2387,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2447,14 +2416,15 @@
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700241-pediasure-peptigro-vainilla-lata-x-850-gr</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2471,27 +2441,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2502,14 +2470,15 @@
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237700013-pediasure-ninos-sabor</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2526,27 +2495,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>8886451012043</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2557,14 +2524,15 @@
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700250-pediasure-peptigro-vainilla-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2581,27 +2549,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2612,14 +2578,15 @@
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237800057-pediasure-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2636,27 +2603,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2667,14 +2632,15 @@
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850020-pediasure-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2691,27 +2657,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2722,14 +2686,15 @@
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224650221-pediasure-peptigro-fresa-lata-x-850-gr</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2746,27 +2711,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>8710428021885</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2777,14 +2740,15 @@
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/235100241-pediasure-10-sabor-vainilla-lata-x-850-gr</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2801,27 +2765,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2832,14 +2794,15 @@
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700233-pediasure-peptigro-fresa-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2856,27 +2819,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2887,14 +2848,15 @@
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239750129-pediasure-vainilla-rpb</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2911,27 +2873,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2942,14 +2902,15 @@
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/236750203-pediasure-liquido-upage-10-sabor-vainilla-frasco-x-220-ml</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -2966,27 +2927,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" s="2" t="inlineStr">
         <is>
           <t>5099864016987</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2997,14 +2956,15 @@
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700107-formula-infantil-similac-1-5-hmo-0-6-meses-lata-x-350-gr</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3021,27 +2981,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>5099864016994</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3052,14 +3010,15 @@
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700115-formula-infantil-similac-1-5-hmo-0-6-meses-lata-x-800-gr</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3076,27 +3035,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3107,14 +3064,15 @@
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700086-formula-infantil-similac-1-5-hmo-0-6-meses-caja-x-1400-gr</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3131,27 +3089,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>7703186497345</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3162,14 +3118,15 @@
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/278600465-formula-infantil-similac</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3186,27 +3143,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>5099864017021</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3217,14 +3172,15 @@
       <c r="M50" t="n">
         <v>0</v>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850076-formula-infantil-similac-2-6-meses-5hmo-lata-x-1800-gr</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3241,27 +3197,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>7703186502186</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3272,14 +3226,15 @@
       <c r="M51" t="n">
         <v>0</v>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850050-formula-infantil-similac-2-6-meses-5-hmo-caja-x-1400-gr</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3296,27 +3251,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>5099864017007</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -3327,14 +3280,15 @@
       <c r="M52" t="n">
         <v>0</v>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850092-formula-infantil-similac-2-6-meses-5-hmo-lata-x-350-gr</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3351,27 +3305,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -3382,14 +3334,15 @@
       <c r="M53" t="n">
         <v>0</v>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264800087-formula-infantil-similac-3-5-hmo-lata-x-1800-gr</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3406,27 +3359,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -3437,14 +3388,15 @@
       <c r="M54" t="n">
         <v>0</v>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850113-formula-infantil-similac-3-5-hmo-lata-x-800-gr</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3461,27 +3413,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -3492,14 +3442,15 @@
       <c r="M55" t="n">
         <v>0</v>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264800095-formula-infantil-similac-3-5-hmo-lata-x-350-gr</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3516,27 +3467,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t>7703186029508</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -3547,14 +3496,15 @@
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1043377-leche-en-polvo-similac</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3571,27 +3521,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr">
         <is>
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -3602,14 +3550,15 @@
       <c r="M57" t="n">
         <v>0</v>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1037373-formula-infantil-similac-prematuros</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3626,27 +3575,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -3657,14 +3604,15 @@
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/263800018-formula-infantil-similac-rice-0-12-meses-x-400-gr</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3681,27 +3629,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -3712,14 +3658,15 @@
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1013041-formula-infantil-similac</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3736,27 +3683,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr">
         <is>
           <t>8427030008820</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3767,14 +3712,15 @@
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/293350505-formula-infantil-similac-total-comfort-2-prosensitive-lata-x-820-gr</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3791,27 +3737,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -3822,14 +3766,15 @@
       <c r="M61" t="n">
         <v>0</v>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1053211-formula-infantil-similac-etapa-1</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3846,27 +3791,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr">
         <is>
           <t>8427030009285</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -3877,14 +3820,15 @@
       <c r="M62" t="n">
         <v>0</v>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/244800207-formula-infantil-similac-total-comfort-5hmos-etapa-1-x-800-gr</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
@@ -3901,27 +3845,25 @@
           <t>Farmatodo</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
           <t>8427030009278</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>0</v>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3932,21 +3874,22 @@
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/244750203-formula-infantil-similac-total-comfort-5hmos-etapa-1-x-350-gr</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>NO DISPONIBLE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q63"/>
+  <autoFilter ref="A1:R63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>